--- a/artfynd/A 29039-2026 artfynd.xlsx
+++ b/artfynd/A 29039-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135406614</v>
       </c>
       <c r="B2" t="n">
-        <v>96859</v>
+        <v>96861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135406587</v>
       </c>
       <c r="B3" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>135406626</v>
       </c>
       <c r="B4" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29039-2026 artfynd.xlsx
+++ b/artfynd/A 29039-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135406614</v>
       </c>
       <c r="B2" t="n">
-        <v>96861</v>
+        <v>96878</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135406587</v>
       </c>
       <c r="B3" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>135406626</v>
       </c>
       <c r="B4" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>135406652</v>
       </c>
       <c r="B5" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
